--- a/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen asma</t>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,65</t>
+          <t>2,05; 8,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,46</t>
+          <t>1,42; 7,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 14,74</t>
+          <t>2,73; 14,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,66</t>
+          <t>0,78; 7,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 11,23</t>
+          <t>1,29; 11,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,42</t>
+          <t>0,84; 10,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,9</t>
+          <t>1,86; 6,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,79</t>
+          <t>1,92; 7,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,05</t>
+          <t>1,95; 7,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,41</t>
+          <t>0,78; 6,77</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,16</t>
+          <t>1,61; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,42</t>
+          <t>1,21; 3,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,49</t>
+          <t>1,2; 3,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,85</t>
+          <t>1,1; 3,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,55</t>
+          <t>1,44; 3,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,5</t>
+          <t>1,35; 3,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,05</t>
+          <t>1,72; 4,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,31</t>
+          <t>2,32; 5,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,36</t>
+          <t>1,74; 3,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,06</t>
+          <t>1,52; 3,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,32</t>
+          <t>1,76; 3,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,0</t>
+          <t>2,02; 4,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,3</t>
+          <t>1,44; 6,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,73</t>
+          <t>0,31; 2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,07</t>
+          <t>0,9; 5,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,93</t>
+          <t>1,66; 7,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,28; 6,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,99</t>
+          <t>1,06; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 11,6</t>
+          <t>0,92; 10,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,7</t>
+          <t>2,11; 5,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,21</t>
+          <t>0,79; 3,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,32</t>
+          <t>0,9; 3,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,81</t>
+          <t>1,25; 6,87</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,27</t>
+          <t>2,04; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,88</t>
+          <t>1,2; 2,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,3</t>
+          <t>1,48; 3,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,33</t>
+          <t>1,36; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,85</t>
+          <t>1,78; 3,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,79</t>
+          <t>1,94; 3,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,74</t>
+          <t>1,71; 3,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,44</t>
+          <t>2,26; 5,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,65</t>
+          <t>2,2; 3,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,01</t>
+          <t>1,67; 3,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,2</t>
+          <t>1,8; 3,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,94</t>
+          <t>2,09; 3,95</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3912</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6659</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7165</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5397</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1866; 7817</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7120</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1620; 8500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3968</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>680; 6545</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1082; 9453</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4795</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>523; 6340</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3307; 11963</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3377; 13294</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2494; 10159</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>916; 7899</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10973</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9470</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9894</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10963</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18532</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>21936</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20688</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23122</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>28425</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6711; 17211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5451; 16226</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5659; 16239</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5039; 15995</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6850; 17571</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6648; 17767</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8393; 20436</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12011; 27539</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15522; 30714</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>14311; 28919</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>16897; 32498</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19759; 39430</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5650</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3457</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6316</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11216</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9772</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2505; 10721</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2213</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>534; 4772</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1353; 7800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2630; 11104</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2196; 10441</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1990; 9568</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1679; 18583</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7024; 18031</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10677</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3244; 11627</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4174; 22880</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20535</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13448</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>39811</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35014</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>41255</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13883; 28151</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8489; 20761</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10432; 24039</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9030; 22358</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12866; 26579</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14505; 28522</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12716; 26725</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>17244; 40171</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>30860; 51874</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>24357; 44839</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>26154; 46007</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>29872; 56304</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,6</t>
+          <t>1,49; 8,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,75</t>
+          <t>1,45; 9,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,31</t>
+          <t>3,04; 15,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,54</t>
+          <t>0,8; 7,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,32</t>
+          <t>1,29; 11,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 10,23</t>
+          <t>0,85; 11,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,73</t>
+          <t>1,91; 6,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,58</t>
+          <t>2,04; 7,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,94</t>
+          <t>1,94; 7,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,77</t>
+          <t>0,67; 6,1</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,14</t>
+          <t>1,58; 4,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,61</t>
+          <t>1,18; 3,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,44</t>
+          <t>1,17; 3,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,48</t>
+          <t>1,18; 3,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,68</t>
+          <t>1,4; 3,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,6</t>
+          <t>1,44; 3,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,18</t>
+          <t>1,61; 4,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,33</t>
+          <t>2,21; 5,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,44</t>
+          <t>1,69; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,07</t>
+          <t>1,48; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,38</t>
+          <t>1,68; 3,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,04</t>
+          <t>2,05; 4,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,16</t>
+          <t>1,57; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,76</t>
+          <t>0,31; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,22</t>
+          <t>0,84; 5,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,02</t>
+          <t>1,69; 6,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,09</t>
+          <t>1,29; 5,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,1</t>
+          <t>1,04; 4,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,14</t>
+          <t>0,93; 12,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,43</t>
+          <t>2,0; 5,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,17</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,23</t>
+          <t>0,88; 3,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,87</t>
+          <t>1,34; 7,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,13</t>
+          <t>2,15; 4,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,94</t>
+          <t>1,11; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,41</t>
+          <t>1,49; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,37</t>
+          <t>1,31; 3,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,68</t>
+          <t>1,82; 3,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,81</t>
+          <t>1,84; 3,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,59</t>
+          <t>1,79; 3,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,27</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,7</t>
+          <t>2,14; 3,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,08</t>
+          <t>1,72; 3,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,17</t>
+          <t>1,78; 3,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,95</t>
+          <t>2,19; 4,07</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1866; 7817</t>
+          <t>1358; 8082</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1306; 7120</t>
+          <t>1330; 8488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1620; 8500</t>
+          <t>1807; 9171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3968</t>
+          <t>0; 3827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>680; 6545</t>
+          <t>692; 6218</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1082; 9453</t>
+          <t>1076; 9383</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4795</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>523; 6340</t>
+          <t>524; 6867</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3307; 11963</t>
+          <t>3389; 11977</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3377; 13294</t>
+          <t>3572; 13419</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2494; 10159</t>
+          <t>2484; 10190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>916; 7899</t>
+          <t>783; 7120</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6711; 17211</t>
+          <t>6579; 17331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5451; 16226</t>
+          <t>5290; 15971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5659; 16239</t>
+          <t>5542; 16291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5039; 15995</t>
+          <t>5429; 16165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6850; 17571</t>
+          <t>6698; 16930</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6648; 17767</t>
+          <t>7104; 17748</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8393; 20436</t>
+          <t>7889; 20020</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12011; 27539</t>
+          <t>11403; 27808</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15522; 30714</t>
+          <t>15134; 30519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14311; 28919</t>
+          <t>13956; 30052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16897; 32498</t>
+          <t>16179; 32732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19759; 39430</t>
+          <t>20019; 39709</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2505; 10721</t>
+          <t>2726; 10905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2213</t>
+          <t>0; 2537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534; 4772</t>
+          <t>529; 4776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1353; 7800</t>
+          <t>1260; 7822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2630; 11104</t>
+          <t>2678; 10375</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2196; 10441</t>
+          <t>2206; 10184</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1990; 9568</t>
+          <t>1952; 9075</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1679; 18583</t>
+          <t>1700; 22132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7024; 18031</t>
+          <t>6640; 18394</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2657; 10677</t>
+          <t>2645; 10623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3244; 11627</t>
+          <t>3163; 11867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4174; 22880</t>
+          <t>4460; 23758</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13883; 28151</t>
+          <t>14626; 28995</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8489; 20761</t>
+          <t>7856; 20292</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10432; 24039</t>
+          <t>10516; 23805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9030; 22358</t>
+          <t>8702; 21576</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12866; 26579</t>
+          <t>13150; 27321</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14505; 28522</t>
+          <t>13784; 28168</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12716; 26725</t>
+          <t>13327; 27885</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17244; 40171</t>
+          <t>18728; 41195</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30860; 51874</t>
+          <t>29996; 51112</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24357; 44839</t>
+          <t>25055; 45019</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26154; 46007</t>
+          <t>25800; 44912</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29872; 56304</t>
+          <t>31169; 58098</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,3%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,89</t>
+          <t>0,8; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 9,24</t>
+          <t>0,83; 11,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 15,44</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,92; 10,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,16</t>
+          <t>1,47; 8,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,23</t>
+          <t>1,41; 8,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>3,15; 14,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 11,08</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,74</t>
+          <t>2,15; 6,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,65</t>
+          <t>1,94; 7,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,96</t>
+          <t>1,95; 8,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,1</t>
+          <t>0,86; 7,23</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,17</t>
+          <t>1,29; 3,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,55</t>
+          <t>1,35; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,45</t>
+          <t>1,72; 4,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,52</t>
+          <t>2,32; 5,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,55</t>
+          <t>1,59; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,6</t>
+          <t>1,2; 3,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,1</t>
+          <t>1,26; 3,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,38</t>
+          <t>1,36; 4,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,42</t>
+          <t>1,75; 3,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,19</t>
+          <t>1,49; 3,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,41</t>
+          <t>1,64; 3,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,07</t>
+          <t>2,12; 4,18</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,26</t>
+          <t>1,69; 6,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,77</t>
+          <t>1,05; 4,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,23</t>
+          <t>0,57; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,56</t>
+          <t>1,51; 6,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,94</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,84</t>
+          <t>0,32; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 12,07</t>
+          <t>0,95; 5,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,54</t>
+          <t>2,18; 5,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,75; 3,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,29</t>
+          <t>0,89; 3,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,14</t>
+          <t>1,11; 4,26</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,26</t>
+          <t>1,86; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,87</t>
+          <t>1,84; 3,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,38</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,25</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,78</t>
+          <t>2,1; 4,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,77</t>
+          <t>1,16; 2,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,74</t>
+          <t>1,42; 3,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>1,46; 3,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,64</t>
+          <t>2,25; 3,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,09</t>
+          <t>1,72; 3,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,1</t>
+          <t>1,82; 3,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,07</t>
+          <t>2,12; 3,77</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3912</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3535</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4112</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3629</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>803</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3186</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1358; 8082</t>
+          <t>694; 6650</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1330; 8488</t>
+          <t>689; 9384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1807; 9171</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3827</t>
+          <t>522; 6160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>692; 6218</t>
+          <t>1337; 7864</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1076; 9383</t>
+          <t>1295; 7769</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>1868; 8753</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>524; 6867</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3389; 11977</t>
+          <t>3819; 12264</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3572; 13419</t>
+          <t>3411; 13657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2484; 10190</t>
+          <t>2493; 10308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>783; 7120</t>
+          <t>888; 7487</t>
         </is>
       </c>
     </row>
@@ -1581,37 +1581,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10963</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17481</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10973</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9470</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9910</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9894</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10963</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11218</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13212</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>27612</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6579; 17331</t>
+          <t>6152; 16913</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5290; 15971</t>
+          <t>6674; 17264</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5542; 16291</t>
+          <t>8412; 19790</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5429; 16165</t>
+          <t>11035; 25791</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6698; 16930</t>
+          <t>6599; 17295</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7104; 17748</t>
+          <t>5414; 15392</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7889; 20020</t>
+          <t>5946; 16505</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11403; 27808</t>
+          <t>5856; 17885</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15134; 30519</t>
+          <t>15587; 29993</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13956; 30052</t>
+          <t>14058; 28884</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16179; 32732</t>
+          <t>15716; 31890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20019; 39709</t>
+          <t>19272; 37881</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5650</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5567</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5166</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>7368</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2726; 10905</t>
+          <t>2667; 10952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2537</t>
+          <t>2219; 10242</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>529; 4776</t>
+          <t>1968; 9355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1260; 7822</t>
+          <t>966; 9270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2678; 10375</t>
+          <t>2629; 10973</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2206; 10184</t>
+          <t>0; 2143</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1952; 9075</t>
+          <t>547; 4721</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1700; 22132</t>
+          <t>1420; 8051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6640; 18394</t>
+          <t>7252; 18924</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2645; 10623</t>
+          <t>2538; 10802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3163; 11867</t>
+          <t>3205; 11949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4460; 23758</t>
+          <t>3521; 13573</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14626; 28995</t>
+          <t>13446; 27793</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7856; 20292</t>
+          <t>13791; 28380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10516; 23805</t>
+          <t>13025; 27863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8702; 21576</t>
+          <t>16067; 33293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13150; 27321</t>
+          <t>14301; 29054</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13784; 28168</t>
+          <t>8232; 20330</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13327; 27885</t>
+          <t>10036; 23232</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18728; 41195</t>
+          <t>9164; 23163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29996; 51112</t>
+          <t>31636; 51250</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25055; 45019</t>
+          <t>25046; 43822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25800; 44912</t>
+          <t>26405; 46378</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31169; 58098</t>
+          <t>28238; 50149</t>
         </is>
       </c>
     </row>
